--- a/tools/importer/reports/import-about-us.report.xlsx
+++ b/tools/importer/reports/import-about-us.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-03-28T18:54:48.099Z</t>
+    <t>2026-04-01T00:34:28.466Z</t>
   </si>
   <si>
     <t>About Us: Starbucks Coffee Company</t>
